--- a/portal/repositorio/ABL/MATRIZ_ABL.xlsx
+++ b/portal/repositorio/ABL/MATRIZ_ABL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8222668d6376a54f/Mentecreativa/Power BI/1- CARGA DE CAMPAÑAS/ABL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1128" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B07D10D9-16DB-4324-8879-8494F5707F46}"/>
+  <xr:revisionPtr revIDLastSave="1467" documentId="13_ncr:1_{3A8FC570-0B2A-4238-83E4-F9F0A98B9035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F799A17-FE57-448F-8DEB-BAE7290B74D2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7452C65D-6E1C-43BD-8F12-28ED56C392EB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5548" uniqueCount="1675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5732" uniqueCount="1742">
   <si>
     <t>TRADE</t>
   </si>
@@ -5068,6 +5068,207 @@
   </si>
   <si>
     <t>Milo Saborizantes y Lacteos</t>
+  </si>
+  <si>
+    <t>W33 HIPER LIDER - CALDOS WALMART (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W33 HIPER LIDER - CAMPAÑA MCKAY (GLORIFICADOR POP UP)</t>
+  </si>
+  <si>
+    <t>W33 HIPER LIDER - NESTLE ESENCIAL (HUINCHA)</t>
+  </si>
+  <si>
+    <t>W33 HIPER LIDER - NESTLE ESENCIAL (LAT CABECERA)</t>
+  </si>
+  <si>
+    <t>W33 HIPER LIDER - NESTLE ESENCIAL (STOPPER)</t>
+  </si>
+  <si>
+    <t>W33 JUMBO - NESTLE ESENCIAL (LAT CABECERA)</t>
+  </si>
+  <si>
+    <t>W33 JUMBO - NESTLE ESENCIAL (MARCO PUERTA)</t>
+  </si>
+  <si>
+    <t>W33 JUMBO - NESTLE ESENCIAL (STOPPER)</t>
+  </si>
+  <si>
+    <t>W33 LIDER EXPRESS - TRAFICO NATURNES (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W33 LIDER EXPRESS - TRAFICO NATURNES (STOPPER)</t>
+  </si>
+  <si>
+    <t>W33 SSRR - CHILENIDAD SSRR (REV. CABECERAS)</t>
+  </si>
+  <si>
+    <t>W33 SSRR - MES DE LA CHILENIDAD (ISLA)</t>
+  </si>
+  <si>
+    <t>W33 SSRR - NESTLE ESENCIAL (FLEJERA)</t>
+  </si>
+  <si>
+    <t>W33 SSRR - NESTLE ESENCIAL (STOPPER)</t>
+  </si>
+  <si>
+    <t>W34 HIPER LIDER - JALEA CENTELLA (STOPPER)</t>
+  </si>
+  <si>
+    <t>W34 HIPER LIDER - LISTA TRAFICO WM (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W34 JUMBO - FIRE SAHNE NUSS (LATERAL COLGANTE)</t>
+  </si>
+  <si>
+    <t>W34 JUMBO - FIRE SAHNE NUSS (STOPPER)</t>
+  </si>
+  <si>
+    <t>W34 TOTTUS - FIRE SAHNE NUSS (STOPPER)</t>
+  </si>
+  <si>
+    <t>W34 SISA - JALEA CENTELLA (STOPPER)</t>
+  </si>
+  <si>
+    <t>W34 JUMBO - JALEA CENTELLA (STOPPER)</t>
+  </si>
+  <si>
+    <t>JALEA CENTELLA</t>
+  </si>
+  <si>
+    <t>Fire Sahne Nuss</t>
+  </si>
+  <si>
+    <t>Lista Trafico WM</t>
+  </si>
+  <si>
+    <t>Trafico Wm</t>
+  </si>
+  <si>
+    <t>Campaña escencial Jumbo</t>
+  </si>
+  <si>
+    <t>Campaña escencial SSRR</t>
+  </si>
+  <si>
+    <t>Campaña escencial</t>
+  </si>
+  <si>
+    <t>Chilenidad SSRR</t>
+  </si>
+  <si>
+    <t>Payloader Caldos Walmart</t>
+  </si>
+  <si>
+    <t>Caldos</t>
+  </si>
+  <si>
+    <t>Coffee Mate</t>
+  </si>
+  <si>
+    <t>Mes de la Chilenidad</t>
+  </si>
+  <si>
+    <t>W33 HIPER LIDER - MES DE LA CHILENIDAD (ISLA)</t>
+  </si>
+  <si>
+    <t>W33 HIPER LIDER - COFFEE MATE (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W34 WALMART - PLAN PIÑA WM (CUBRE CABECERA)</t>
+  </si>
+  <si>
+    <t>W34 WALMART - PLAN PIÑA WM (HUINCHA)</t>
+  </si>
+  <si>
+    <t>W34 WALMART - PLAN PIÑA WM (CHUPON)</t>
+  </si>
+  <si>
+    <t>W34 JUMBO - PLAN PIÑA JUMBO (VIBRIN)</t>
+  </si>
+  <si>
+    <t>W34 JUMBO - PLAN PIÑA JUMBO (MARCO REFRI)</t>
+  </si>
+  <si>
+    <t>W34 JUMBO - PLAN PIÑA JUMBO (LOMO NAVE)</t>
+  </si>
+  <si>
+    <t>W34 JUMBO - PLAN PIÑA JUMBO (CUBRE CABECERA)</t>
+  </si>
+  <si>
+    <t>W34 SISA - PLAN PIÑA SISA (VIBRIN)</t>
+  </si>
+  <si>
+    <t>W34 SISA - PLAN PIÑA SISA (MARCO REFRI)</t>
+  </si>
+  <si>
+    <t>W34 SISA - PLAN PIÑA SISA (LOMO NAVE)</t>
+  </si>
+  <si>
+    <t>W34 SSRR - PLAN PIÑA SSRR (STOPPER SSRR)</t>
+  </si>
+  <si>
+    <t>W34 SSRR - PLAN PIÑA SSRR (VIBRIN REDONDO)</t>
+  </si>
+  <si>
+    <t>W34 SSRR - PLAN PIÑA SSRR (NAVE CABECERA)</t>
+  </si>
+  <si>
+    <t>W34 TOTTUS - PLAN PIÑA TOTTUS (STOPPER)</t>
+  </si>
+  <si>
+    <t>W34 TOTTUS - PLAN PIÑA TOTTUS (CENEFA)</t>
+  </si>
+  <si>
+    <t>W34 TOTTUS - PLAN PIÑA TOTTUS (STICKER)</t>
+  </si>
+  <si>
+    <t>W34 TOTTUS - PLAN PIÑA TOTTUS (CABECERA)</t>
+  </si>
+  <si>
+    <t>W34 TOTTUS - FIRE SAHNE NUSS (COLGANTE)</t>
+  </si>
+  <si>
+    <t>Plan Piña Jumbo</t>
+  </si>
+  <si>
+    <t>Plan Piña Tottus</t>
+  </si>
+  <si>
+    <t>Plan Piña WM</t>
+  </si>
+  <si>
+    <t>Plan Piña SISA</t>
+  </si>
+  <si>
+    <t>Plan Piña</t>
+  </si>
+  <si>
+    <t>Lista Trafico Acuenta</t>
+  </si>
+  <si>
+    <t>W35 ACUENTA - LISTA DE TRAFICO (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>Reposicion Payloader Milo</t>
+  </si>
+  <si>
+    <t>PDQ Leche Condensada</t>
+  </si>
+  <si>
+    <t>W35 HIPER LIDER - REPOSICION MILO (PAYLOADER)</t>
+  </si>
+  <si>
+    <t>W35 SISA - CHILENIDAD SISA (CUBREPALLET)</t>
+  </si>
+  <si>
+    <t>W38 TOTTUS - CAMPAÑA ESENCIAL TOTTUS (CABECERA)</t>
+  </si>
+  <si>
+    <t>W38 TOTTUS - CAMPAÑA ESENCIAL TOTTUS (STOPPER)</t>
+  </si>
+  <si>
+    <t>Campaña Esencial Tottus</t>
   </si>
 </sst>
 </file>
@@ -8880,7 +9081,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9999E96D-4CFB-4E05-B33D-24F4D0D91426}">
   <sheetPr codeName="Hoja1" filterMode="1"/>
-  <dimension ref="A1:K1482"/>
+  <dimension ref="A1:K1528"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -43991,7 +44192,7 @@
         <v>46303</v>
       </c>
       <c r="G1478" s="24">
-        <f t="shared" ref="G1478:G1482" si="27">WORKDAY.INTL(F1478,10,1,0)+1</f>
+        <f t="shared" ref="G1478:G1486" si="27">WORKDAY.INTL(F1478,10,1,0)+1</f>
         <v>46318</v>
       </c>
       <c r="H1478" t="s">
@@ -44104,6 +44305,1215 @@
       </c>
       <c r="H1482" t="s">
         <v>1670</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:8">
+      <c r="A1483" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D1483" s="25">
+        <v>46262</v>
+      </c>
+      <c r="E1483" s="25">
+        <v>46298</v>
+      </c>
+      <c r="F1483" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1483" s="24">
+        <f t="shared" si="27"/>
+        <v>46318</v>
+      </c>
+      <c r="H1483" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:8">
+      <c r="A1484" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1484" s="25">
+        <v>46244</v>
+      </c>
+      <c r="E1484" s="25">
+        <v>46248</v>
+      </c>
+      <c r="F1484" s="25">
+        <v>46280</v>
+      </c>
+      <c r="G1484" s="24">
+        <f t="shared" si="27"/>
+        <v>46295</v>
+      </c>
+      <c r="H1484" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:8">
+      <c r="A1485" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D1485" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1485" s="25">
+        <v>46261</v>
+      </c>
+      <c r="F1485" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1485" s="24">
+        <f t="shared" si="27"/>
+        <v>46318</v>
+      </c>
+      <c r="H1485" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:8">
+      <c r="A1486" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D1486" s="25">
+        <v>46254</v>
+      </c>
+      <c r="F1486" s="25">
+        <v>46288</v>
+      </c>
+      <c r="G1486" s="24">
+        <f t="shared" si="27"/>
+        <v>46303</v>
+      </c>
+      <c r="H1486" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:8">
+      <c r="A1487" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D1487" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1487" s="25">
+        <v>46261</v>
+      </c>
+      <c r="F1487" s="25">
+        <v>46295</v>
+      </c>
+      <c r="G1487" s="24">
+        <f t="shared" ref="G1487:G1496" si="28">WORKDAY.INTL(F1487,10,1,0)+1</f>
+        <v>46310</v>
+      </c>
+      <c r="H1487" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:8">
+      <c r="A1488" s="18" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1488" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D1488" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1488" s="25">
+        <v>46261</v>
+      </c>
+      <c r="F1488" s="25">
+        <v>46295</v>
+      </c>
+      <c r="G1488" s="24">
+        <f t="shared" si="28"/>
+        <v>46310</v>
+      </c>
+      <c r="H1488" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:8">
+      <c r="A1489" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1489" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D1489" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1489" s="25">
+        <v>46266</v>
+      </c>
+      <c r="F1489" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1489" s="24">
+        <f t="shared" si="28"/>
+        <v>46308</v>
+      </c>
+      <c r="H1489" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:8">
+      <c r="A1490" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1490" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D1490" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1490" s="25">
+        <v>46266</v>
+      </c>
+      <c r="F1490" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1490" s="24">
+        <f t="shared" si="28"/>
+        <v>46308</v>
+      </c>
+      <c r="H1490" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:8">
+      <c r="A1491" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1491" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D1491" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1491" s="25">
+        <v>46266</v>
+      </c>
+      <c r="F1491" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1491" s="24">
+        <f t="shared" si="28"/>
+        <v>46308</v>
+      </c>
+      <c r="H1491" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:8">
+      <c r="A1492" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1492" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D1492" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1492" s="25">
+        <v>46266</v>
+      </c>
+      <c r="F1492" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1492" s="24">
+        <f t="shared" si="28"/>
+        <v>46308</v>
+      </c>
+      <c r="H1492" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:8">
+      <c r="A1493" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1493" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D1493" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1493" s="25">
+        <v>46266</v>
+      </c>
+      <c r="F1493" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1493" s="24">
+        <f t="shared" si="28"/>
+        <v>46308</v>
+      </c>
+      <c r="H1493" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:8">
+      <c r="A1494" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1494" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D1494" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1494" s="25">
+        <v>46266</v>
+      </c>
+      <c r="F1494" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1494" s="24">
+        <f t="shared" si="28"/>
+        <v>46318</v>
+      </c>
+      <c r="H1494" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:8">
+      <c r="A1495" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1495" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D1495" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1495" s="25">
+        <v>46266</v>
+      </c>
+      <c r="F1495" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1495" s="24">
+        <f t="shared" si="28"/>
+        <v>46318</v>
+      </c>
+      <c r="H1495" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:8">
+      <c r="A1496" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1496" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D1496" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1496" s="25">
+        <v>46266</v>
+      </c>
+      <c r="F1496" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1496" s="24">
+        <f t="shared" si="28"/>
+        <v>46318</v>
+      </c>
+      <c r="H1496" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:8">
+      <c r="A1497" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C1497" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D1497" s="25">
+        <v>46254</v>
+      </c>
+      <c r="F1497" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1497" s="24">
+        <f t="shared" ref="G1497:G1502" si="29">WORKDAY.INTL(F1497,10,1,0)+1</f>
+        <v>46318</v>
+      </c>
+      <c r="H1497" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:8">
+      <c r="A1498" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D1498" s="25">
+        <v>46254</v>
+      </c>
+      <c r="F1498" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1498" s="24">
+        <f t="shared" si="29"/>
+        <v>46318</v>
+      </c>
+      <c r="H1498" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:8">
+      <c r="A1499" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D1499" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1499" s="25">
+        <v>46261</v>
+      </c>
+      <c r="F1499" s="25">
+        <v>46302</v>
+      </c>
+      <c r="G1499" s="24">
+        <f t="shared" si="29"/>
+        <v>46317</v>
+      </c>
+      <c r="H1499" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:8">
+      <c r="A1500" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D1500" s="25">
+        <v>46259</v>
+      </c>
+      <c r="F1500" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1500" s="24">
+        <f t="shared" si="29"/>
+        <v>46308</v>
+      </c>
+      <c r="H1500" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:8">
+      <c r="A1501" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D1501" s="25">
+        <v>46259</v>
+      </c>
+      <c r="F1501" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1501" s="24">
+        <f t="shared" si="29"/>
+        <v>46308</v>
+      </c>
+      <c r="H1501" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:8">
+      <c r="A1502" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1502" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D1502" s="25">
+        <v>46259</v>
+      </c>
+      <c r="F1502" s="25">
+        <v>46286</v>
+      </c>
+      <c r="G1502" s="24">
+        <f t="shared" si="29"/>
+        <v>46301</v>
+      </c>
+      <c r="H1502" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:8">
+      <c r="A1503" s="18" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1503" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D1503" s="25">
+        <v>46259</v>
+      </c>
+      <c r="F1503" s="25">
+        <v>46286</v>
+      </c>
+      <c r="G1503" s="24">
+        <f t="shared" ref="G1503" si="30">WORKDAY.INTL(F1503,10,1,0)+1</f>
+        <v>46301</v>
+      </c>
+      <c r="H1503" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:8">
+      <c r="A1504" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1504" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D1504" s="25">
+        <v>46254</v>
+      </c>
+      <c r="F1504" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1504" s="24">
+        <f t="shared" ref="G1504:G1509" si="31">WORKDAY.INTL(F1504,10,1,0)+1</f>
+        <v>46318</v>
+      </c>
+      <c r="H1504" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:8">
+      <c r="A1505" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1505" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1505" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D1505" s="25">
+        <v>46259</v>
+      </c>
+      <c r="F1505" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1505" s="24">
+        <f t="shared" si="31"/>
+        <v>46308</v>
+      </c>
+      <c r="H1505" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:8">
+      <c r="A1506" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1506" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D1506" s="25">
+        <v>46259</v>
+      </c>
+      <c r="F1506" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1506" s="24">
+        <f t="shared" si="31"/>
+        <v>46308</v>
+      </c>
+      <c r="H1506" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:8">
+      <c r="A1507" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1507" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1507" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D1507" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1507" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1507" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1507" s="24">
+        <f t="shared" si="31"/>
+        <v>46318</v>
+      </c>
+      <c r="H1507" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:8">
+      <c r="A1508" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1508" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1508" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D1508" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1508" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1508" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1508" s="24">
+        <f t="shared" si="31"/>
+        <v>46318</v>
+      </c>
+      <c r="H1508" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:8">
+      <c r="A1509" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1509" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1509" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D1509" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1509" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1509" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1509" s="24">
+        <f t="shared" si="31"/>
+        <v>46318</v>
+      </c>
+      <c r="H1509" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:8">
+      <c r="A1510" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1510" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D1510" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1510" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1510" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1510" s="24">
+        <f t="shared" ref="G1510:G1528" si="32">WORKDAY.INTL(F1510,10,1,0)+1</f>
+        <v>46308</v>
+      </c>
+      <c r="H1510" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:8">
+      <c r="A1511" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1511" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D1511" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1511" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1511" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1511" s="24">
+        <f t="shared" si="32"/>
+        <v>46308</v>
+      </c>
+      <c r="H1511" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:8">
+      <c r="A1512" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1512" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1512" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D1512" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1512" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1512" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1512" s="24">
+        <f t="shared" si="32"/>
+        <v>46308</v>
+      </c>
+      <c r="H1512" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:8">
+      <c r="A1513" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1513" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1513" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D1513" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1513" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1513" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1513" s="24">
+        <f t="shared" si="32"/>
+        <v>46308</v>
+      </c>
+      <c r="H1513" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:8">
+      <c r="A1514" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1514" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1514" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D1514" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1514" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1514" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1514" s="24">
+        <f t="shared" si="32"/>
+        <v>46308</v>
+      </c>
+      <c r="H1514" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:8">
+      <c r="A1515" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1515" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1515" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D1515" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1515" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1515" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1515" s="24">
+        <f t="shared" si="32"/>
+        <v>46308</v>
+      </c>
+      <c r="H1515" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:8">
+      <c r="A1516" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1516" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1516" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D1516" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1516" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1516" s="25">
+        <v>46293</v>
+      </c>
+      <c r="G1516" s="24">
+        <f t="shared" si="32"/>
+        <v>46308</v>
+      </c>
+      <c r="H1516" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:8">
+      <c r="A1517" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1517" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1517" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D1517" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1517" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1517" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1517" s="24">
+        <f t="shared" si="32"/>
+        <v>46318</v>
+      </c>
+      <c r="H1517" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:8">
+      <c r="A1518" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1518" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1518" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D1518" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1518" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1518" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1518" s="24">
+        <f t="shared" si="32"/>
+        <v>46318</v>
+      </c>
+      <c r="H1518" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:8">
+      <c r="A1519" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1519" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1519" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D1519" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1519" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1519" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1519" s="24">
+        <f t="shared" si="32"/>
+        <v>46318</v>
+      </c>
+      <c r="H1519" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:8">
+      <c r="A1520" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1520" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1520" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D1520" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1520" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1520" s="25">
+        <v>46286</v>
+      </c>
+      <c r="G1520" s="24">
+        <f t="shared" si="32"/>
+        <v>46301</v>
+      </c>
+      <c r="H1520" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:8">
+      <c r="A1521" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1521" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D1521" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1521" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1521" s="25">
+        <v>46286</v>
+      </c>
+      <c r="G1521" s="24">
+        <f t="shared" si="32"/>
+        <v>46301</v>
+      </c>
+      <c r="H1521" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:8">
+      <c r="A1522" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1522" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D1522" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1522" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1522" s="25">
+        <v>46286</v>
+      </c>
+      <c r="G1522" s="24">
+        <f t="shared" si="32"/>
+        <v>46301</v>
+      </c>
+      <c r="H1522" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:8">
+      <c r="A1523" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1523" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D1523" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1523" s="25">
+        <v>46272</v>
+      </c>
+      <c r="F1523" s="25">
+        <v>46286</v>
+      </c>
+      <c r="G1523" s="24">
+        <f t="shared" si="32"/>
+        <v>46301</v>
+      </c>
+      <c r="H1523" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:8">
+      <c r="A1524" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1524" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D1524" s="25">
+        <v>46254</v>
+      </c>
+      <c r="E1524" s="25">
+        <v>46261</v>
+      </c>
+      <c r="F1524" s="25">
+        <v>46302</v>
+      </c>
+      <c r="G1524" s="24">
+        <f t="shared" si="32"/>
+        <v>46317</v>
+      </c>
+      <c r="H1524" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:8">
+      <c r="A1525" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1525" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D1525" s="25">
+        <v>46254</v>
+      </c>
+      <c r="F1525" s="25">
+        <v>46303</v>
+      </c>
+      <c r="G1525" s="24">
+        <f t="shared" si="32"/>
+        <v>46318</v>
+      </c>
+      <c r="H1525" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:8">
+      <c r="A1526" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1526" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D1526" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1526" s="25">
+        <v>46262</v>
+      </c>
+      <c r="F1526" s="25">
+        <v>46294</v>
+      </c>
+      <c r="G1526" s="24">
+        <f t="shared" si="32"/>
+        <v>46309</v>
+      </c>
+      <c r="H1526" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:8">
+      <c r="A1527" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1527" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D1527" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1527" s="25">
+        <v>46266</v>
+      </c>
+      <c r="F1527" s="25">
+        <v>46316</v>
+      </c>
+      <c r="G1527" s="24">
+        <f t="shared" si="32"/>
+        <v>46331</v>
+      </c>
+      <c r="H1527" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:8">
+      <c r="A1528" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B1528" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D1528" s="25">
+        <v>46259</v>
+      </c>
+      <c r="E1528" s="25">
+        <v>46266</v>
+      </c>
+      <c r="F1528" s="25">
+        <v>46316</v>
+      </c>
+      <c r="G1528" s="24">
+        <f t="shared" si="32"/>
+        <v>46331</v>
+      </c>
+      <c r="H1528" t="s">
+        <v>1740</v>
       </c>
     </row>
   </sheetData>
